--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.64093631494099</v>
+        <v>2.21665215117791</v>
       </c>
       <c r="D2" t="n">
-        <v>13.77572399989234</v>
+        <v>2.238555149982505</v>
       </c>
       <c r="E2" t="n">
-        <v>15.90561745353932</v>
+        <v>2.58466283620014</v>
       </c>
       <c r="F2" t="n">
-        <v>15.82279431349281</v>
+        <v>2.571204075942581</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.22421368699401</v>
+        <v>3.123934724136527</v>
       </c>
       <c r="D3" t="n">
-        <v>19.35088565728564</v>
+        <v>3.144518919308917</v>
       </c>
       <c r="E3" t="n">
-        <v>15.90561745353932</v>
+        <v>2.58466283620014</v>
       </c>
       <c r="F3" t="n">
-        <v>15.82279431349281</v>
+        <v>2.571204075942581</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5.253519759927681</v>
+        <v>0.8536969609882483</v>
       </c>
       <c r="D4" t="n">
-        <v>5.380742504806178</v>
+        <v>0.8743706570310039</v>
       </c>
       <c r="E4" t="n">
-        <v>15.90561745353932</v>
+        <v>2.58466283620014</v>
       </c>
       <c r="F4" t="n">
-        <v>15.82279431349281</v>
+        <v>2.571204075942581</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.73221090792374</v>
+        <v>3.856484272537609</v>
       </c>
       <c r="D5" t="n">
-        <v>23.59866982172776</v>
+        <v>3.834783846030761</v>
       </c>
       <c r="E5" t="n">
-        <v>15.90561745353932</v>
+        <v>2.58466283620014</v>
       </c>
       <c r="F5" t="n">
-        <v>15.82279431349281</v>
+        <v>2.571204075942581</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.54004497668426</v>
+        <v>5.287757308711192</v>
       </c>
       <c r="D6" t="n">
-        <v>32.4543754023955</v>
+        <v>5.273836002889269</v>
       </c>
       <c r="E6" t="n">
-        <v>15.90561745353932</v>
+        <v>2.58466283620014</v>
       </c>
       <c r="F6" t="n">
-        <v>15.82279431349281</v>
+        <v>2.571204075942581</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.74409586900202</v>
+        <v>4.995915578712829</v>
       </c>
       <c r="D7" t="n">
-        <v>30.6066173615557</v>
+        <v>4.973575321252802</v>
       </c>
       <c r="E7" t="n">
-        <v>15.90561745353932</v>
+        <v>2.58466283620014</v>
       </c>
       <c r="F7" t="n">
-        <v>15.82279431349281</v>
+        <v>2.571204075942581</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>62.08374019053635</v>
+        <v>10.08860778096216</v>
       </c>
       <c r="D8" t="n">
-        <v>62.13455828429802</v>
+        <v>10.09686572119843</v>
       </c>
       <c r="E8" t="n">
-        <v>15.90561745353932</v>
+        <v>2.58466283620014</v>
       </c>
       <c r="F8" t="n">
-        <v>15.82279431349281</v>
+        <v>2.571204075942581</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>44.81599903108243</v>
+        <v>7.282599842550894</v>
       </c>
       <c r="D9" t="n">
-        <v>44.53598893636861</v>
+        <v>7.237098202159899</v>
       </c>
       <c r="E9" t="n">
-        <v>15.90561745353932</v>
+        <v>2.58466283620014</v>
       </c>
       <c r="F9" t="n">
-        <v>15.82279431349281</v>
+        <v>2.571204075942581</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>45.53123410317393</v>
+        <v>7.398825541765763</v>
       </c>
       <c r="D10" t="n">
-        <v>45.21008901551745</v>
+        <v>7.346639465021585</v>
       </c>
       <c r="E10" t="n">
-        <v>15.90561745353932</v>
+        <v>2.58466283620014</v>
       </c>
       <c r="F10" t="n">
-        <v>15.82279431349281</v>
+        <v>2.571204075942581</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87705439986721</v>
+        <v>5.342521339978421</v>
       </c>
       <c r="D11" t="n">
-        <v>32.82372094755301</v>
+        <v>5.333854653977365</v>
       </c>
       <c r="E11" t="n">
-        <v>15.90561745353932</v>
+        <v>2.58466283620014</v>
       </c>
       <c r="F11" t="n">
-        <v>15.82279431349281</v>
+        <v>2.571204075942581</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
